--- a/3-能力管理/运行记录类文件/JXTX-03-06-运维服务能力管理指标完成情况.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-06-运维服务能力管理指标完成情况.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9060"/>
+    <workbookView windowWidth="23040" windowHeight="9060"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="96">
   <si>
     <t>编号</t>
   </si>
@@ -87,6 +87,9 @@
     <t>半年度</t>
   </si>
   <si>
+    <t>-</t>
+  </si>
+  <si>
     <t>客户投诉次数</t>
   </si>
   <si>
@@ -96,13 +99,16 @@
     <t>年度</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>0次</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>0</t>
     </r>
     <r>
@@ -126,6 +132,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>1</t>
     </r>
     <r>
@@ -322,10 +334,16 @@
     <t>12条</t>
   </si>
   <si>
-    <t>18条%</t>
+    <t>18条</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
       <t>15</t>
     </r>
     <r>
@@ -351,7 +369,30 @@
     <t>服务数据分析利用次数</t>
   </si>
   <si>
-    <t>≥次</t>
+    <t>3次</t>
+  </si>
+  <si>
+    <t>4次</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="Consolas"/>
+        <charset val="134"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FF0F1115"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>次</t>
+    </r>
   </si>
   <si>
     <t>交付</t>
@@ -364,6 +405,11 @@
   </si>
   <si>
     <t>项目应急演练次数</t>
+  </si>
+  <si>
+    <t>说明：针对10月份变更成功率不达标现象，进行以下改进
+1.对相关运维人员进行培训，学习变更管理制度
+2.后期质量管理人员对此进行抽查，杜绝此类事件再次发生</t>
   </si>
 </sst>
 </file>
@@ -376,7 +422,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -400,6 +446,17 @@
       <sz val="10.5"/>
       <color rgb="FF0F1115"/>
       <name val="Consolas"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -766,7 +823,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -898,35 +955,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -1028,28 +1056,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1058,122 +1077,131 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1183,12 +1211,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1234,67 +1256,37 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="57" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1694,11 +1686,11 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="4.77777777777778" style="3" customWidth="1"/>
+    <col min="2" max="2" width="4.77777777777778" style="1" customWidth="1"/>
     <col min="3" max="3" width="10.7777777777778" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
     <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
@@ -1706,1437 +1698,1940 @@
     <col min="7" max="10" width="11.6666666666667" customWidth="1"/>
     <col min="11" max="15" width="11.6666666666667"/>
     <col min="16" max="17" width="12.8888888888889"/>
-    <col min="18" max="18" width="9.44444444444444" style="4"/>
+    <col min="18" max="18" width="9.44444444444444" style="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.75" customHeight="1" spans="1:18">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7"/>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="10"/>
-      <c r="I1" s="10"/>
-      <c r="J1" s="10"/>
-      <c r="K1" s="10"/>
-      <c r="L1" s="10"/>
-      <c r="M1" s="10"/>
-      <c r="N1" s="10"/>
-      <c r="O1" s="10"/>
-      <c r="P1" s="10"/>
-      <c r="Q1" s="11"/>
-      <c r="R1" s="12" t="s">
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
+      <c r="J1" s="8"/>
+      <c r="K1" s="8"/>
+      <c r="L1" s="8"/>
+      <c r="M1" s="8"/>
+      <c r="N1" s="8"/>
+      <c r="O1" s="8"/>
+      <c r="P1" s="8"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="10" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" ht="24.75" customHeight="1" spans="1:18">
-      <c r="A2" s="13"/>
-      <c r="B2" s="14"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="17">
+      <c r="A2" s="11"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="15">
         <v>45658</v>
       </c>
-      <c r="H2" s="17">
+      <c r="H2" s="15">
         <v>45689</v>
       </c>
-      <c r="I2" s="17">
+      <c r="I2" s="15">
         <v>45717</v>
       </c>
-      <c r="J2" s="17">
+      <c r="J2" s="15">
         <v>45748</v>
       </c>
-      <c r="K2" s="17">
+      <c r="K2" s="15">
         <v>45778</v>
       </c>
-      <c r="L2" s="17">
+      <c r="L2" s="15">
         <v>45809</v>
       </c>
-      <c r="M2" s="17">
+      <c r="M2" s="15">
         <v>45839</v>
       </c>
-      <c r="N2" s="17">
+      <c r="N2" s="15">
         <v>45870</v>
       </c>
-      <c r="O2" s="17">
+      <c r="O2" s="15">
         <v>45901</v>
       </c>
-      <c r="P2" s="17">
+      <c r="P2" s="15">
         <v>45931</v>
       </c>
-      <c r="Q2" s="17">
+      <c r="Q2" s="15">
         <v>45962</v>
       </c>
-      <c r="R2" s="18"/>
+      <c r="R2" s="16"/>
     </row>
     <row r="3" spans="1:18">
-      <c r="A3" s="19">
+      <c r="A3" s="17">
         <f>ROW()-2</f>
         <v>1</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22" t="s">
+      <c r="C3" s="18"/>
+      <c r="D3" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
+      <c r="G3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L3" s="21">
+        <v>0.97</v>
+      </c>
+      <c r="M3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q3" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R3" s="21">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="4" spans="1:18">
-      <c r="A4" s="19">
+      <c r="A4" s="17">
         <f t="shared" ref="A4:A13" si="0">ROW()-2</f>
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="22" t="s">
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="E4" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q4" s="4" t="s">
+      <c r="G4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P4" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q4" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="R4" s="25" t="s">
+      <c r="R4" s="22" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:18">
-      <c r="A5" s="19">
+      <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="22" t="s">
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="F5" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="4" t="s">
+      <c r="G5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P5" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="R5" s="25" t="s">
+      <c r="R5" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:18">
-      <c r="A6" s="19">
+      <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="27"/>
-      <c r="D6" s="22" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="F6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="P6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q6" s="4" t="s">
+      <c r="G6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P6" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q6" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="R6" s="25" t="s">
+      <c r="R6" s="22" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:18">
-      <c r="A7" s="19">
+      <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="30">
-        <v>1</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L7" s="30">
-        <v>1</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O7" s="30">
-        <v>1</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R7" s="31" cm="1">
+      <c r="G7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="21">
+        <v>1</v>
+      </c>
+      <c r="J7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="21">
+        <v>1</v>
+      </c>
+      <c r="M7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O7" s="21">
+        <v>1</v>
+      </c>
+      <c r="P7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q7" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R7" s="23" cm="1">
         <f t="array" ref="R7">SUMPRODUCT(--(0&amp;SUBSTITUTE(G7:Q7,"-","0")))/IF(F7="季度",3,IF(F7="月度",11,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:18">
-      <c r="A8" s="19">
+      <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="18"/>
+      <c r="C8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I8" s="30">
-        <v>1</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="30">
-        <v>1</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O8" s="30">
-        <v>1</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q8" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R8" s="31" cm="1">
+      <c r="G8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I8" s="21">
+        <v>1</v>
+      </c>
+      <c r="J8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L8" s="21">
+        <v>1</v>
+      </c>
+      <c r="M8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O8" s="21">
+        <v>1</v>
+      </c>
+      <c r="P8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q8" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R8" s="23" cm="1">
         <f t="array" ref="R8">SUMPRODUCT(--(0&amp;SUBSTITUTE(G8:Q8,"-","0")))/IF(F8="季度",3,IF(F8="月度",11,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18">
-      <c r="A9" s="19">
+      <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="B9" s="32"/>
-      <c r="C9" s="29" t="s">
+      <c r="B9" s="18"/>
+      <c r="C9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I9" s="30">
-        <v>1</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="30">
-        <v>1</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O9" s="30">
-        <v>1</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q9" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R9" s="31" cm="1">
+      <c r="G9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I9" s="21">
+        <v>1</v>
+      </c>
+      <c r="J9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="21">
+        <v>1</v>
+      </c>
+      <c r="M9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O9" s="21">
+        <v>1</v>
+      </c>
+      <c r="P9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R9" s="23" cm="1">
         <f t="array" ref="R9">SUMPRODUCT(--(0&amp;SUBSTITUTE(G9:Q9,"-","0")))/IF(F9="季度",3,IF(F9="月度",11,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:18">
-      <c r="A10" s="19">
+      <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="B10" s="32"/>
-      <c r="C10" s="29" t="s">
+      <c r="B10" s="18"/>
+      <c r="C10" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="30">
-        <v>1</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="30">
-        <v>1</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O10" s="30">
-        <v>1</v>
-      </c>
-      <c r="P10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R10" s="31" cm="1">
+      <c r="G10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I10" s="21">
+        <v>1</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L10" s="21">
+        <v>1</v>
+      </c>
+      <c r="M10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O10" s="21">
+        <v>1</v>
+      </c>
+      <c r="P10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q10" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R10" s="23" cm="1">
         <f t="array" ref="R10">SUMPRODUCT(--(0&amp;SUBSTITUTE(G10:Q10,"-","0")))/IF(F10="季度",3,IF(F10="月度",11,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:18">
-      <c r="A11" s="19">
+      <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="B11" s="32"/>
-      <c r="C11" s="29" t="s">
+      <c r="B11" s="18"/>
+      <c r="C11" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I11" s="30">
-        <v>1</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="30">
-        <v>1</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O11" s="30">
-        <v>1</v>
-      </c>
-      <c r="P11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R11" s="31" cm="1">
+      <c r="G11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I11" s="21">
+        <v>1</v>
+      </c>
+      <c r="J11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L11" s="21">
+        <v>1</v>
+      </c>
+      <c r="M11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O11" s="21">
+        <v>1</v>
+      </c>
+      <c r="P11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q11" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R11" s="23" cm="1">
         <f t="array" ref="R11">SUMPRODUCT(--(0&amp;SUBSTITUTE(G11:Q11,"-","0")))/IF(F11="季度",3,IF(F11="月度",11,1))</f>
         <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:18">
-      <c r="A12" s="19">
+      <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="29" t="s">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="F12" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I12" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L12" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O12" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="P12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q12" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R12" s="31" cm="1">
-        <f t="array" ref="R12">SUMPRODUCT(--(0&amp;SUBSTITUTE(G12:Q12,"-","0")))/IF(F12="季度",3,IF(F12="月度",11,1))</f>
-        <v>0</v>
+      <c r="G12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I12" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O12" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q12" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R12" s="23" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:18">
-      <c r="A13" s="19">
+      <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="29" t="s">
+      <c r="C13" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G13" s="4"/>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="31" cm="1">
-        <f t="array" ref="R13">SUMPRODUCT(--(0&amp;SUBSTITUTE(G13:Q13,"-","0")))/IF(F13="季度",3,IF(F13="月度",11,1))</f>
-        <v>0</v>
+      <c r="F13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O13" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P13" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q13" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="R13" s="23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:18">
-      <c r="A14" s="19">
+      <c r="A14" s="17">
         <f t="shared" ref="A14:A23" si="1">ROW()-2</f>
         <v>12</v>
       </c>
-      <c r="B14" s="32"/>
-      <c r="C14" s="29" t="s">
+      <c r="B14" s="18"/>
+      <c r="C14" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G14" s="4"/>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4"/>
-      <c r="J14" s="4"/>
-      <c r="K14" s="34"/>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="31" cm="1">
+      <c r="G14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I14" s="21">
+        <v>1</v>
+      </c>
+      <c r="J14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L14" s="21">
+        <v>1</v>
+      </c>
+      <c r="M14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O14" s="21">
+        <v>1</v>
+      </c>
+      <c r="P14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q14" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R14" s="23" cm="1">
         <f t="array" ref="R14">SUMPRODUCT(--(0&amp;SUBSTITUTE(G14:Q14,"-","0")))/IF(F14="季度",3,IF(F14="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:18">
-      <c r="A15" s="19">
+      <c r="A15" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
       </c>
-      <c r="B15" s="32"/>
-      <c r="C15" s="29" t="s">
+      <c r="B15" s="18"/>
+      <c r="C15" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4"/>
-      <c r="I15" s="4"/>
-      <c r="J15" s="4"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="31" cm="1">
+      <c r="G15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="21">
+        <v>1</v>
+      </c>
+      <c r="J15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="21">
+        <v>1</v>
+      </c>
+      <c r="M15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O15" s="21">
+        <v>1</v>
+      </c>
+      <c r="P15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q15" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R15" s="23" cm="1">
         <f t="array" ref="R15">SUMPRODUCT(--(0&amp;SUBSTITUTE(G15:Q15,"-","0")))/IF(F15="季度",3,IF(F15="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:18">
-      <c r="A16" s="19">
+      <c r="A16" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
       </c>
-      <c r="B16" s="32"/>
-      <c r="C16" s="28" t="s">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="31" cm="1">
+      <c r="G16" s="21">
+        <v>1</v>
+      </c>
+      <c r="H16" s="21">
+        <v>1</v>
+      </c>
+      <c r="I16" s="21">
+        <v>1</v>
+      </c>
+      <c r="J16" s="21">
+        <v>1</v>
+      </c>
+      <c r="K16" s="21">
+        <v>1</v>
+      </c>
+      <c r="L16" s="21">
+        <v>1</v>
+      </c>
+      <c r="M16" s="21">
+        <v>1</v>
+      </c>
+      <c r="N16" s="21">
+        <v>1</v>
+      </c>
+      <c r="O16" s="21">
+        <v>1</v>
+      </c>
+      <c r="P16" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="21">
+        <v>1</v>
+      </c>
+      <c r="R16" s="23" cm="1">
         <f t="array" ref="R16">SUMPRODUCT(--(0&amp;SUBSTITUTE(G16:Q16,"-","0")))/IF(F16="季度",3,IF(F16="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:18">
-      <c r="A17" s="19">
+      <c r="A17" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
       </c>
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="22" t="s">
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4"/>
-      <c r="I17" s="4"/>
-      <c r="J17" s="4"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="31" cm="1">
+      <c r="G17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I17" s="21">
+        <v>1</v>
+      </c>
+      <c r="J17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L17" s="21">
+        <v>1</v>
+      </c>
+      <c r="M17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O17" s="21">
+        <v>1</v>
+      </c>
+      <c r="P17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q17" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R17" s="23" cm="1">
         <f t="array" ref="R17">SUMPRODUCT(--(0&amp;SUBSTITUTE(G17:Q17,"-","0")))/IF(F17="季度",3,IF(F17="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:18">
-      <c r="A18" s="19">
+      <c r="A18" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
       </c>
-      <c r="B18" s="32"/>
-      <c r="C18" s="28" t="s">
+      <c r="B18" s="18"/>
+      <c r="C18" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G18" s="4"/>
-      <c r="H18" s="4"/>
-      <c r="I18" s="4"/>
-      <c r="J18" s="4"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4"/>
-      <c r="R18" s="31" cm="1">
+      <c r="G18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18" s="21">
+        <v>0.9</v>
+      </c>
+      <c r="J18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L18" s="21">
+        <v>0.92</v>
+      </c>
+      <c r="M18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O18" s="21">
+        <v>1</v>
+      </c>
+      <c r="P18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q18" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R18" s="23" cm="1">
         <f t="array" ref="R18">SUMPRODUCT(--(0&amp;SUBSTITUTE(G18:Q18,"-","0")))/IF(F18="季度",3,IF(F18="月度",11,1))</f>
-        <v>0</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="19" spans="1:18">
-      <c r="A19" s="19">
+      <c r="A19" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
       </c>
-      <c r="B19" s="32"/>
-      <c r="C19" s="33"/>
-      <c r="D19" s="22" t="s">
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4"/>
-      <c r="I19" s="4"/>
-      <c r="J19" s="4"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-      <c r="Q19" s="4"/>
-      <c r="R19" s="31" cm="1">
+      <c r="G19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="21">
+        <v>0.92</v>
+      </c>
+      <c r="J19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L19" s="21">
+        <v>1</v>
+      </c>
+      <c r="M19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O19" s="21">
+        <v>0.98</v>
+      </c>
+      <c r="P19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q19" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R19" s="23" cm="1">
         <f t="array" ref="R19">SUMPRODUCT(--(0&amp;SUBSTITUTE(G19:Q19,"-","0")))/IF(F19="季度",3,IF(F19="月度",11,1))</f>
-        <v>0</v>
+        <v>0.966666666666667</v>
       </c>
     </row>
     <row r="20" spans="1:18">
-      <c r="A20" s="19">
+      <c r="A20" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
       </c>
-      <c r="B20" s="32"/>
-      <c r="C20" s="29" t="s">
+      <c r="B20" s="18"/>
+      <c r="C20" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G20" s="4"/>
-      <c r="H20" s="4"/>
-      <c r="I20" s="4"/>
-      <c r="J20" s="4"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="31" cm="1">
+      <c r="G20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I20" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L20" s="21">
+        <v>1</v>
+      </c>
+      <c r="M20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O20" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q20" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R20" s="23" cm="1">
         <f t="array" ref="R20">SUMPRODUCT(--(0&amp;SUBSTITUTE(G20:Q20,"-","0")))/IF(F20="季度",3,IF(F20="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:18">
-      <c r="A21" s="19">
+      <c r="A21" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
       </c>
-      <c r="B21" s="32"/>
-      <c r="C21" s="29" t="s">
+      <c r="B21" s="18"/>
+      <c r="C21" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G21" s="4"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="4"/>
-      <c r="J21" s="4"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="31" cm="1">
+      <c r="G21" s="21">
+        <v>0.98</v>
+      </c>
+      <c r="H21" s="21">
+        <v>0.98</v>
+      </c>
+      <c r="I21" s="21">
+        <v>1</v>
+      </c>
+      <c r="J21" s="21">
+        <v>1</v>
+      </c>
+      <c r="K21" s="21">
+        <v>1</v>
+      </c>
+      <c r="L21" s="21">
+        <v>1</v>
+      </c>
+      <c r="M21" s="21">
+        <v>1</v>
+      </c>
+      <c r="N21" s="21">
+        <v>1</v>
+      </c>
+      <c r="O21" s="21">
+        <v>1</v>
+      </c>
+      <c r="P21" s="24">
+        <v>0.95</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>0.98</v>
+      </c>
+      <c r="R21" s="23" cm="1">
         <f t="array" ref="R21">SUMPRODUCT(--(0&amp;SUBSTITUTE(G21:Q21,"-","0")))/IF(F21="季度",3,IF(F21="月度",11,1))</f>
-        <v>0</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="22" spans="1:18">
-      <c r="A22" s="19">
+      <c r="A22" s="17">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="B22" s="32"/>
-      <c r="C22" s="29" t="s">
+      <c r="B22" s="18"/>
+      <c r="C22" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G22" s="4"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="4"/>
-      <c r="J22" s="4"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="31" cm="1">
+      <c r="G22" s="21">
+        <v>1</v>
+      </c>
+      <c r="H22" s="21">
+        <v>1</v>
+      </c>
+      <c r="I22" s="21">
+        <v>1</v>
+      </c>
+      <c r="J22" s="21">
+        <v>1</v>
+      </c>
+      <c r="K22" s="21">
+        <v>1</v>
+      </c>
+      <c r="L22" s="21">
+        <v>1</v>
+      </c>
+      <c r="M22" s="21">
+        <v>1</v>
+      </c>
+      <c r="N22" s="21">
+        <v>1</v>
+      </c>
+      <c r="O22" s="21">
+        <v>1</v>
+      </c>
+      <c r="P22" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="21">
+        <v>1</v>
+      </c>
+      <c r="R22" s="23" cm="1">
         <f t="array" ref="R22">SUMPRODUCT(--(0&amp;SUBSTITUTE(G22:Q22,"-","0")))/IF(F22="季度",3,IF(F22="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:18">
-      <c r="A23" s="19">
+      <c r="A23" s="17">
         <f t="shared" si="1"/>
         <v>21</v>
       </c>
-      <c r="B23" s="32"/>
-      <c r="C23" s="28" t="s">
+      <c r="B23" s="18"/>
+      <c r="C23" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="31" cm="1">
+      <c r="G23" s="21">
+        <v>1</v>
+      </c>
+      <c r="H23" s="21">
+        <v>1</v>
+      </c>
+      <c r="I23" s="21">
+        <v>1</v>
+      </c>
+      <c r="J23" s="21">
+        <v>1</v>
+      </c>
+      <c r="K23" s="21">
+        <v>1</v>
+      </c>
+      <c r="L23" s="21">
+        <v>1</v>
+      </c>
+      <c r="M23" s="21">
+        <v>1</v>
+      </c>
+      <c r="N23" s="21">
+        <v>1</v>
+      </c>
+      <c r="O23" s="21">
+        <v>1</v>
+      </c>
+      <c r="P23" s="21">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="21">
+        <v>1</v>
+      </c>
+      <c r="R23" s="23" cm="1">
         <f t="array" ref="R23">SUMPRODUCT(--(0&amp;SUBSTITUTE(G23:Q23,"-","0")))/IF(F23="季度",3,IF(F23="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:18">
-      <c r="A24" s="19">
+      <c r="A24" s="17">
         <f t="shared" ref="A24:A35" si="2">ROW()-2</f>
         <v>22</v>
       </c>
-      <c r="B24" s="32"/>
-      <c r="C24" s="33"/>
-      <c r="D24" s="22" t="s">
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-      <c r="J24" s="4"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="31" cm="1">
-        <f t="array" ref="R24">SUMPRODUCT(--(0&amp;SUBSTITUTE(G24:Q24,"-","0")))/IF(F24="季度",3,IF(F24="月度",11,1))</f>
-        <v>0</v>
+      <c r="G24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="J24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="K24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="L24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="M24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="N24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="O24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="P24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q24" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="R24" s="23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:18">
-      <c r="A25" s="19">
+      <c r="A25" s="17">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="29" t="s">
+      <c r="B25" s="18"/>
+      <c r="C25" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G25" s="4"/>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4"/>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="4"/>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-      <c r="Q25" s="4"/>
-      <c r="R25" s="31" cm="1">
-        <f t="array" ref="R25">SUMPRODUCT(--(0&amp;SUBSTITUTE(G25:Q25,"-","0")))/IF(F25="季度",3,IF(F25="月度",11,1))</f>
-        <v>0</v>
+      <c r="F25" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O25" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q25" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="R25" s="23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:18">
-      <c r="A26" s="19">
+      <c r="A26" s="17">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B26" s="33"/>
-      <c r="C26" s="29" t="s">
+      <c r="B26" s="18"/>
+      <c r="C26" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="F26" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G26" s="4"/>
-      <c r="H26" s="4"/>
-      <c r="I26" s="4"/>
-      <c r="J26" s="4"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="4"/>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-      <c r="Q26" s="4"/>
-      <c r="R26" s="31" cm="1">
-        <f t="array" ref="R26">SUMPRODUCT(--(0&amp;SUBSTITUTE(G26:Q26,"-","0")))/IF(F26="季度",3,IF(F26="月度",11,1))</f>
-        <v>0</v>
+      <c r="F26" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I26" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="J26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L26" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O26" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="P26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q26" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="R26" s="23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:18">
-      <c r="A27" s="19">
+      <c r="A27" s="17">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="C27" s="21"/>
-      <c r="D27" s="22" t="s">
+      <c r="C27" s="18"/>
+      <c r="D27" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="E27" s="22" t="s">
+      <c r="E27" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="F27" s="22" t="s">
+      <c r="F27" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="2"/>
-      <c r="R27" s="31" cm="1">
+      <c r="G27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I27" s="21">
+        <v>1</v>
+      </c>
+      <c r="J27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="21">
+        <v>1</v>
+      </c>
+      <c r="M27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O27" s="21">
+        <v>1</v>
+      </c>
+      <c r="P27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q27" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R27" s="23" cm="1">
         <f t="array" ref="R27">SUMPRODUCT(--(0&amp;SUBSTITUTE(G27:Q27,"-","0")))/IF(F27="季度",3,IF(F27="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" s="1" customFormat="1" spans="1:18">
-      <c r="A28" s="19">
+      <c r="A28" s="17">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B28" s="26"/>
-      <c r="C28" s="27"/>
-      <c r="D28" s="22" t="s">
+      <c r="B28" s="18"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="E28" s="22" t="s">
+      <c r="E28" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="F28" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
-      <c r="P28" s="2"/>
-      <c r="Q28" s="2"/>
-      <c r="R28" s="31" cm="1">
+      <c r="F28" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P28" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q28" s="21">
+        <v>0.94</v>
+      </c>
+      <c r="R28" s="23" cm="1">
         <f t="array" ref="R28">SUMPRODUCT(--(0&amp;SUBSTITUTE(G28:Q28,"-","0")))/IF(F28="季度",3,IF(F28="月度",11,1))</f>
-        <v>0</v>
+        <v>0.94</v>
       </c>
     </row>
     <row r="29" s="1" customFormat="1" spans="1:18">
-      <c r="A29" s="19">
+      <c r="A29" s="17">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C29" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D29" s="22" t="s">
+      <c r="D29" s="19" t="s">
         <v>74</v>
       </c>
-      <c r="E29" s="22" t="s">
+      <c r="E29" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="F29" s="22" t="s">
+      <c r="F29" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-      <c r="I29" s="2"/>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
-      <c r="P29" s="2"/>
-      <c r="Q29" s="2"/>
-      <c r="R29" s="31" cm="1">
+      <c r="G29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I29" s="21">
+        <v>1</v>
+      </c>
+      <c r="J29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L29" s="21">
+        <v>1</v>
+      </c>
+      <c r="M29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O29" s="21">
+        <v>1</v>
+      </c>
+      <c r="P29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q29" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R29" s="23" cm="1">
         <f t="array" ref="R29">SUMPRODUCT(--(0&amp;SUBSTITUTE(G29:Q29,"-","0")))/IF(F29="季度",3,IF(F29="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" s="1" customFormat="1" spans="1:18">
-      <c r="A30" s="19">
+      <c r="A30" s="17">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B30" s="32"/>
-      <c r="C30" s="29" t="s">
+      <c r="B30" s="18"/>
+      <c r="C30" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D30" s="22" t="s">
+      <c r="D30" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="E30" s="22" t="s">
+      <c r="E30" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="F30" s="22" t="s">
+      <c r="F30" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I30" s="35">
+      <c r="G30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I30" s="21">
         <v>0.9</v>
       </c>
-      <c r="J30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L30" s="35">
+      <c r="J30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L30" s="21">
         <v>0.92</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O30" s="35">
+      <c r="M30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O30" s="21">
         <v>0.95</v>
       </c>
-      <c r="P30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q30" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R30" s="31" cm="1">
+      <c r="P30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R30" s="23" cm="1">
         <f t="array" ref="R30">SUMPRODUCT(--(0&amp;SUBSTITUTE(G30:Q30,"-","0")))/IF(F30="季度",3,IF(F30="月度",11,1))</f>
         <v>0.923333333333333</v>
       </c>
     </row>
     <row r="31" s="1" customFormat="1" spans="1:18">
-      <c r="A31" s="19">
+      <c r="A31" s="17">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B31" s="32"/>
-      <c r="C31" s="29" t="s">
+      <c r="B31" s="18"/>
+      <c r="C31" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D31" s="22" t="s">
+      <c r="D31" s="19" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="22" t="s">
+      <c r="E31" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="F31" s="22" t="s">
+      <c r="F31" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I31" s="36" t="s">
+      <c r="G31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I31" s="26" t="s">
         <v>80</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L31" s="35" t="s">
+      <c r="J31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L31" s="21" t="s">
         <v>81</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="O31" s="35" t="s">
+      <c r="M31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O31" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="P31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q31" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R31" s="37" t="s">
+      <c r="P31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q31" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R31" s="23" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:18">
-      <c r="A32" s="19">
+      <c r="A32" s="17">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B32" s="32"/>
-      <c r="C32" s="29" t="s">
+      <c r="B32" s="18"/>
+      <c r="C32" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D32" s="22" t="s">
+      <c r="D32" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="E32" s="22" t="s">
+      <c r="E32" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F32" s="22" t="s">
+      <c r="F32" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="31" cm="1">
-        <f t="array" ref="R32">SUMPRODUCT(--(0&amp;SUBSTITUTE(G32:Q32,"-","0")))/IF(F32="季度",3,IF(F32="月度",11,1))</f>
-        <v>0</v>
+      <c r="G32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L32" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="M32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R32" s="23" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="33" spans="1:18">
-      <c r="A33" s="19">
+      <c r="A33" s="17">
         <f t="shared" si="2"/>
         <v>31</v>
       </c>
-      <c r="B33" s="33"/>
-      <c r="C33" s="29" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="D33" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="E33" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F33" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I33" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="F33" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="31" cm="1">
-        <f t="array" ref="R33">SUMPRODUCT(--(0&amp;SUBSTITUTE(G33:Q33,"-","0")))/IF(F33="季度",3,IF(F33="月度",11,1))</f>
-        <v>0</v>
+      <c r="J33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L33" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="M33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O33" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="P33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q33" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R33" s="23" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:18">
-      <c r="A34" s="19">
+      <c r="A34" s="17">
         <f t="shared" si="2"/>
         <v>32</v>
       </c>
-      <c r="B34" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="E34" s="40">
-        <v>1</v>
-      </c>
-      <c r="F34" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="31" cm="1">
+      <c r="B34" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="18"/>
+      <c r="D34" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="E34" s="27">
+        <v>1</v>
+      </c>
+      <c r="F34" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q34" s="21">
+        <v>1</v>
+      </c>
+      <c r="R34" s="23" cm="1">
         <f t="array" ref="R34">SUMPRODUCT(--(0&amp;SUBSTITUTE(G34:Q34,"-","0")))/IF(F34="季度",3,IF(F34="月度",11,1))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:18">
-      <c r="A35" s="19">
+      <c r="A35" s="17">
         <f t="shared" si="2"/>
         <v>33</v>
       </c>
-      <c r="B35" s="38" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="E35" s="22" t="s">
+      <c r="B35" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="18"/>
+      <c r="D35" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="E35" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="F35" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="37" t="s">
+      <c r="F35" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="H35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="I35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="J35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="K35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="L35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="M35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="N35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="O35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="P35" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="Q35" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="R35" s="23" t="s">
         <v>20</v>
       </c>
+    </row>
+    <row r="36" ht="71" customHeight="1" spans="1:18">
+      <c r="A36" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28"/>
+      <c r="P36" s="28"/>
+      <c r="Q36" s="28"/>
+      <c r="R36" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="G1:Q1"/>
     <mergeCell ref="B34:C34"/>
     <mergeCell ref="B35:C35"/>
+    <mergeCell ref="A36:R36"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="B13:B26"/>

--- a/3-能力管理/运行记录类文件/JXTX-03-06-运维服务能力管理指标完成情况.xlsx
+++ b/3-能力管理/运行记录类文件/JXTX-03-06-运维服务能力管理指标完成情况.xlsx
@@ -4,15 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060"/>
+    <workbookView xWindow="240" yWindow="120" windowWidth="23040" windowHeight="9060" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="KPI指标体系" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_GoBack" localSheetId="0">KPI指标体系!#REF!</definedName>
+    <definedName name="_GoBack" localSheetId="0">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr fullCalcOnLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -29,28 +29,6 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="423" uniqueCount="96">
   <si>
@@ -107,6 +85,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>0</t>
@@ -116,6 +95,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -136,6 +116,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>1</t>
@@ -145,6 +126,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -342,6 +324,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>15</t>
@@ -351,6 +334,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>条</t>
@@ -380,6 +364,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="Consolas"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>3</t>
@@ -389,6 +374,7 @@
         <sz val="10.5"/>
         <color rgb="FF0F1115"/>
         <rFont val="宋体"/>
+        <family val="2"/>
         <charset val="134"/>
       </rPr>
       <t>次</t>
@@ -427,66 +413,78 @@
       <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color indexed="8"/>
       <name val="楷体_GB2312"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color indexed="8"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF0F1115"/>
       <name val="Consolas"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <u val="single"/>
       <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -494,6 +492,7 @@
       <sz val="18"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -502,7 +501,7 @@
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -510,6 +509,7 @@
       <sz val="15"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -518,6 +518,7 @@
       <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -526,6 +527,7 @@
       <sz val="11"/>
       <color theme="3"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -533,7 +535,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -541,7 +543,7 @@
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -549,7 +551,7 @@
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -557,14 +559,14 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -572,69 +574,51 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
       <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10.5"/>
       <color rgb="FF0F1115"/>
       <name val="宋体"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor indexed="22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -686,19 +670,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -710,19 +694,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -734,19 +718,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -758,19 +742,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -782,19 +766,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.39998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -806,19 +790,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.79998"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.59999"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.39998"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0C0C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="22"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -829,128 +825,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -966,7 +840,6 @@
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -975,16 +848,14 @@
       <bottom style="medium">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.49998"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -999,7 +870,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1014,7 +884,6 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="double">
@@ -1029,7 +898,6 @@
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1038,7 +906,6 @@
       <bottom style="double">
         <color rgb="FFFF8001"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1049,303 +916,503 @@
       <bottom style="double">
         <color theme="4"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
+      <protection/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0">
+      <alignment/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="29">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="1" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="34" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="34" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="1" fillId="3" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="34" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="57" fontId="1" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="57" fontId="2" fillId="34" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="54">
+    <cellStyle name="Normal" xfId="0"/>
+    <cellStyle name="Percent" xfId="15"/>
+    <cellStyle name="Currency" xfId="16"/>
+    <cellStyle name="Currency [0]" xfId="17"/>
+    <cellStyle name="Comma" xfId="18"/>
+    <cellStyle name="Comma [0]" xfId="19"/>
+    <cellStyle name="千位分隔" xfId="20"/>
+    <cellStyle name="货币" xfId="21"/>
+    <cellStyle name="百分比" xfId="22"/>
+    <cellStyle name="千位分隔[0]" xfId="23"/>
+    <cellStyle name="货币[0]" xfId="24"/>
+    <cellStyle name="超链接" xfId="25"/>
+    <cellStyle name="已访问的超链接" xfId="26"/>
+    <cellStyle name="注释" xfId="27"/>
+    <cellStyle name="警告文本" xfId="28"/>
+    <cellStyle name="标题" xfId="29"/>
+    <cellStyle name="解释性文本" xfId="30"/>
+    <cellStyle name="标题 1" xfId="31"/>
+    <cellStyle name="标题 2" xfId="32"/>
+    <cellStyle name="标题 3" xfId="33"/>
+    <cellStyle name="标题 4" xfId="34"/>
+    <cellStyle name="输入" xfId="35"/>
+    <cellStyle name="输出" xfId="36"/>
+    <cellStyle name="计算" xfId="37"/>
+    <cellStyle name="检查单元格" xfId="38"/>
+    <cellStyle name="链接单元格" xfId="39"/>
+    <cellStyle name="汇总" xfId="40"/>
+    <cellStyle name="好" xfId="41"/>
+    <cellStyle name="差" xfId="42"/>
+    <cellStyle name="适中" xfId="43"/>
+    <cellStyle name="强调文字颜色 1" xfId="44"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="45"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="46"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="47"/>
+    <cellStyle name="强调文字颜色 2" xfId="48"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="49"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="50"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="51"/>
+    <cellStyle name="强调文字颜色 3" xfId="52"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="53"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="54"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="55"/>
+    <cellStyle name="强调文字颜色 4" xfId="56"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="57"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="58"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="59"/>
+    <cellStyle name="强调文字颜色 5" xfId="60"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="61"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="62"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="63"/>
+    <cellStyle name="强调文字颜色 6" xfId="64"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="65"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="66"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="67"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
-    <mruColors>
-      <color rgb="00C0C0C0"/>
-    </mruColors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
   </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1687,21 +1754,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="2" width="4.77777777777778" style="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7777777777778" customWidth="1"/>
+    <col min="2" max="2" width="4.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
     <col min="4" max="4" width="21" customWidth="1"/>
-    <col min="5" max="5" width="8.66666666666667" customWidth="1"/>
+    <col min="5" max="5" width="8.625" customWidth="1"/>
     <col min="6" max="6" width="10.5" customWidth="1"/>
-    <col min="7" max="10" width="11.6666666666667" customWidth="1"/>
-    <col min="11" max="15" width="11.6666666666667"/>
-    <col min="16" max="17" width="12.8888888888889"/>
-    <col min="18" max="18" width="9.44444444444444" style="2"/>
+    <col min="7" max="10" width="11.625" customWidth="1"/>
+    <col min="11" max="15" width="11.625"/>
+    <col min="16" max="17" width="12.875"/>
+    <col min="18" max="18" width="9.5" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24.75" customHeight="1" spans="1:18">
+    <row r="1" spans="1:18" ht="24.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1735,7 +1802,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" ht="24.75" customHeight="1" spans="1:18">
+    <row r="2" spans="1:18" ht="24.75" customHeight="1">
       <c r="A2" s="11"/>
       <c r="B2" s="12"/>
       <c r="C2" s="13"/>
@@ -1777,7 +1844,7 @@
       </c>
       <c r="R2" s="16"/>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" ht="14.4">
       <c r="A3" s="17">
         <f>ROW()-2</f>
         <v>1</v>
@@ -1832,9 +1899,9 @@
         <v>0.97</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" ht="14.4">
       <c r="A4" s="17">
-        <f t="shared" ref="A4:A13" si="0">ROW()-2</f>
+        <f t="shared" si="0" ref="A4:A13">ROW()-2</f>
         <v>2</v>
       </c>
       <c r="B4" s="18"/>
@@ -1885,7 +1952,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" ht="14.4">
       <c r="A5" s="17">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1938,7 +2005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" ht="14.4">
       <c r="A6" s="17">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1991,7 +2058,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" ht="14.4">
       <c r="A7" s="17">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2044,12 +2111,12 @@
       <c r="Q7" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R7" s="23" cm="1">
+      <c r="R7" s="23">
         <f t="array" ref="R7">SUMPRODUCT(--(0&amp;SUBSTITUTE(G7:Q7,"-","0")))/IF(F7="季度",3,IF(F7="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" ht="14.4">
       <c r="A8" s="17">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2100,12 +2167,12 @@
       <c r="Q8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R8" s="23" cm="1">
+      <c r="R8" s="23">
         <f t="array" ref="R8">SUMPRODUCT(--(0&amp;SUBSTITUTE(G8:Q8,"-","0")))/IF(F8="季度",3,IF(F8="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:18" ht="14.4">
       <c r="A9" s="17">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2156,12 +2223,12 @@
       <c r="Q9" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R9" s="23" cm="1">
+      <c r="R9" s="23">
         <f t="array" ref="R9">SUMPRODUCT(--(0&amp;SUBSTITUTE(G9:Q9,"-","0")))/IF(F9="季度",3,IF(F9="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:18" ht="14.4">
       <c r="A10" s="17">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2212,12 +2279,12 @@
       <c r="Q10" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R10" s="23" cm="1">
+      <c r="R10" s="23">
         <f t="array" ref="R10">SUMPRODUCT(--(0&amp;SUBSTITUTE(G10:Q10,"-","0")))/IF(F10="季度",3,IF(F10="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:18">
+    <row r="11" spans="1:18" ht="14.4">
       <c r="A11" s="17">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2268,12 +2335,12 @@
       <c r="Q11" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R11" s="23" cm="1">
+      <c r="R11" s="23">
         <f t="array" ref="R11">SUMPRODUCT(--(0&amp;SUBSTITUTE(G11:Q11,"-","0")))/IF(F11="季度",3,IF(F11="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" ht="14.4">
       <c r="A12" s="17">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2328,7 +2395,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:18">
+    <row r="13" spans="1:18" ht="14.4">
       <c r="A13" s="17">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2385,9 +2452,9 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" ht="14.4">
       <c r="A14" s="17">
-        <f t="shared" ref="A14:A23" si="1">ROW()-2</f>
+        <f t="shared" si="1" ref="A14:A23">ROW()-2</f>
         <v>12</v>
       </c>
       <c r="B14" s="18"/>
@@ -2436,12 +2503,12 @@
       <c r="Q14" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R14" s="23" cm="1">
+      <c r="R14" s="23">
         <f t="array" ref="R14">SUMPRODUCT(--(0&amp;SUBSTITUTE(G14:Q14,"-","0")))/IF(F14="季度",3,IF(F14="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:18">
+    <row r="15" spans="1:18" ht="14.4">
       <c r="A15" s="17">
         <f t="shared" si="1"/>
         <v>13</v>
@@ -2492,12 +2559,12 @@
       <c r="Q15" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R15" s="23" cm="1">
+      <c r="R15" s="23">
         <f t="array" ref="R15">SUMPRODUCT(--(0&amp;SUBSTITUTE(G15:Q15,"-","0")))/IF(F15="季度",3,IF(F15="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:18">
+    <row r="16" spans="1:18" ht="14.4">
       <c r="A16" s="17">
         <f t="shared" si="1"/>
         <v>14</v>
@@ -2548,12 +2615,12 @@
       <c r="Q16" s="21">
         <v>1</v>
       </c>
-      <c r="R16" s="23" cm="1">
+      <c r="R16" s="23">
         <f t="array" ref="R16">SUMPRODUCT(--(0&amp;SUBSTITUTE(G16:Q16,"-","0")))/IF(F16="季度",3,IF(F16="月度",11,1))</f>
-        <v>1</v>
+        <v>0.090909090909090912</v>
       </c>
     </row>
-    <row r="17" spans="1:18">
+    <row r="17" spans="1:18" ht="14.4">
       <c r="A17" s="17">
         <f t="shared" si="1"/>
         <v>15</v>
@@ -2602,12 +2669,12 @@
       <c r="Q17" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R17" s="23" cm="1">
+      <c r="R17" s="23">
         <f t="array" ref="R17">SUMPRODUCT(--(0&amp;SUBSTITUTE(G17:Q17,"-","0")))/IF(F17="季度",3,IF(F17="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" ht="14.4">
       <c r="A18" s="17">
         <f t="shared" si="1"/>
         <v>16</v>
@@ -2632,7 +2699,7 @@
         <v>11</v>
       </c>
       <c r="I18" s="21">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="J18" s="20" t="s">
         <v>11</v>
@@ -2658,12 +2725,12 @@
       <c r="Q18" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R18" s="23" cm="1">
+      <c r="R18" s="23">
         <f t="array" ref="R18">SUMPRODUCT(--(0&amp;SUBSTITUTE(G18:Q18,"-","0")))/IF(F18="季度",3,IF(F18="月度",11,1))</f>
-        <v>0.94</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:18">
+    <row r="19" spans="1:18" ht="14.4">
       <c r="A19" s="17">
         <f t="shared" si="1"/>
         <v>17</v>
@@ -2712,12 +2779,12 @@
       <c r="Q19" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R19" s="23" cm="1">
+      <c r="R19" s="23">
         <f t="array" ref="R19">SUMPRODUCT(--(0&amp;SUBSTITUTE(G19:Q19,"-","0")))/IF(F19="季度",3,IF(F19="月度",11,1))</f>
-        <v>0.966666666666667</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:18">
+    <row r="20" spans="1:18" ht="14.4">
       <c r="A20" s="17">
         <f t="shared" si="1"/>
         <v>18</v>
@@ -2768,12 +2835,12 @@
       <c r="Q20" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R20" s="23" cm="1">
+      <c r="R20" s="23">
         <f t="array" ref="R20">SUMPRODUCT(--(0&amp;SUBSTITUTE(G20:Q20,"-","0")))/IF(F20="季度",3,IF(F20="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:18">
+    <row r="21" spans="1:18" ht="14.4">
       <c r="A21" s="17">
         <f t="shared" si="1"/>
         <v>19</v>
@@ -2824,12 +2891,12 @@
       <c r="Q21" s="25">
         <v>0.98</v>
       </c>
-      <c r="R21" s="23" cm="1">
+      <c r="R21" s="23">
         <f t="array" ref="R21">SUMPRODUCT(--(0&amp;SUBSTITUTE(G21:Q21,"-","0")))/IF(F21="季度",3,IF(F21="月度",11,1))</f>
-        <v>0.99</v>
+        <v>0.089090909090909096</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" ht="14.4">
       <c r="A22" s="17">
         <f t="shared" si="1"/>
         <v>20</v>
@@ -2880,12 +2947,12 @@
       <c r="Q22" s="21">
         <v>1</v>
       </c>
-      <c r="R22" s="23" cm="1">
+      <c r="R22" s="23">
         <f t="array" ref="R22">SUMPRODUCT(--(0&amp;SUBSTITUTE(G22:Q22,"-","0")))/IF(F22="季度",3,IF(F22="月度",11,1))</f>
-        <v>1</v>
+        <v>0.090909090909090912</v>
       </c>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" ht="14.4">
       <c r="A23" s="17">
         <f t="shared" si="1"/>
         <v>21</v>
@@ -2936,14 +3003,14 @@
       <c r="Q23" s="21">
         <v>1</v>
       </c>
-      <c r="R23" s="23" cm="1">
+      <c r="R23" s="23">
         <f t="array" ref="R23">SUMPRODUCT(--(0&amp;SUBSTITUTE(G23:Q23,"-","0")))/IF(F23="季度",3,IF(F23="月度",11,1))</f>
-        <v>1</v>
+        <v>0.090909090909090912</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" ht="14.4">
       <c r="A24" s="17">
-        <f t="shared" ref="A24:A35" si="2">ROW()-2</f>
+        <f t="shared" si="2" ref="A24:A35">ROW()-2</f>
         <v>22</v>
       </c>
       <c r="B24" s="18"/>
@@ -2994,7 +3061,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" ht="14.4">
       <c r="A25" s="17">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -3049,7 +3116,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" ht="14.4">
       <c r="A26" s="17">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -3104,7 +3171,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" s="1" customFormat="1" spans="1:18">
+    <row r="27" spans="1:18" s="1" customFormat="1" ht="14.4">
       <c r="A27" s="17">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -3155,12 +3222,12 @@
       <c r="Q27" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R27" s="23" cm="1">
+      <c r="R27" s="23">
         <f t="array" ref="R27">SUMPRODUCT(--(0&amp;SUBSTITUTE(G27:Q27,"-","0")))/IF(F27="季度",3,IF(F27="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="28" s="1" customFormat="1" spans="1:18">
+    <row r="28" spans="1:18" s="1" customFormat="1" ht="14.4">
       <c r="A28" s="17">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -3209,12 +3276,12 @@
       <c r="Q28" s="21">
         <v>0.94</v>
       </c>
-      <c r="R28" s="23" cm="1">
+      <c r="R28" s="23">
         <f t="array" ref="R28">SUMPRODUCT(--(0&amp;SUBSTITUTE(G28:Q28,"-","0")))/IF(F28="季度",3,IF(F28="月度",11,1))</f>
-        <v>0.94</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="29" s="1" customFormat="1" spans="1:18">
+    <row r="29" spans="1:18" s="1" customFormat="1" ht="14.4">
       <c r="A29" s="17">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -3267,12 +3334,12 @@
       <c r="Q29" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R29" s="23" cm="1">
+      <c r="R29" s="23">
         <f t="array" ref="R29">SUMPRODUCT(--(0&amp;SUBSTITUTE(G29:Q29,"-","0")))/IF(F29="季度",3,IF(F29="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="30" s="1" customFormat="1" spans="1:18">
+    <row r="30" spans="1:18" s="1" customFormat="1" ht="14.4">
       <c r="A30" s="17">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -3297,7 +3364,7 @@
         <v>11</v>
       </c>
       <c r="I30" s="21">
-        <v>0.9</v>
+        <v>0.90</v>
       </c>
       <c r="J30" s="20" t="s">
         <v>11</v>
@@ -3323,12 +3390,12 @@
       <c r="Q30" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="R30" s="23" cm="1">
+      <c r="R30" s="23">
         <f t="array" ref="R30">SUMPRODUCT(--(0&amp;SUBSTITUTE(G30:Q30,"-","0")))/IF(F30="季度",3,IF(F30="月度",11,1))</f>
-        <v>0.923333333333333</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="31" s="1" customFormat="1" spans="1:18">
+    <row r="31" spans="1:18" s="1" customFormat="1" ht="14.4">
       <c r="A31" s="17">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -3383,7 +3450,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" ht="14.4">
       <c r="A32" s="17">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -3438,7 +3505,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:18">
+    <row r="33" spans="1:18" ht="14.4">
       <c r="A33" s="17">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -3493,7 +3560,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="34" spans="1:18">
+    <row r="34" spans="1:18" ht="14.4">
       <c r="A34" s="17">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -3544,12 +3611,12 @@
       <c r="Q34" s="21">
         <v>1</v>
       </c>
-      <c r="R34" s="23" cm="1">
+      <c r="R34" s="23">
         <f t="array" ref="R34">SUMPRODUCT(--(0&amp;SUBSTITUTE(G34:Q34,"-","0")))/IF(F34="季度",3,IF(F34="月度",11,1))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:18">
+    <row r="35" spans="1:18" ht="14.4">
       <c r="A35" s="17">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -3604,7 +3671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" ht="71" customHeight="1" spans="1:18">
+    <row r="36" spans="1:18" ht="71" customHeight="1">
       <c r="A36" s="28" t="s">
         <v>95</v>
       </c>
@@ -3648,7 +3715,7 @@
     <mergeCell ref="B27:C28"/>
   </mergeCells>
   <pageMargins left="0.707638888888889" right="0.511805555555556" top="0.747916666666667" bottom="0.747916666666667" header="0.313888888888889" footer="0.313888888888889"/>
-  <pageSetup paperSize="9" scale="66" fitToHeight="0" orientation="landscape"/>
+  <pageSetup fitToHeight="0" orientation="landscape" paperSize="9" scale="10"/>
   <headerFooter alignWithMargins="0"/>
 </worksheet>
 </file>